--- a/formatted_raw/6-15-24_R16&R21_BR_Dilution.xlsx
+++ b/formatted_raw/6-15-24_R16&R21_BR_Dilution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rowde002\Desktop\Graphs With Gage Version 4\formatted_raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABC63FE5-121D-4097-BABC-920F4E230C3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA99C2FE-9BF5-4EF8-AA76-AF1E3FF93210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6495" yWindow="2010" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Microplate Cycle 1 (0 h)" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="272">
   <si>
     <t>Sample IDs</t>
   </si>
@@ -842,15 +842,6 @@
     <t>NQ-R16-BR-100000</t>
   </si>
   <si>
-    <t>NQ-R16-BR-100001</t>
-  </si>
-  <si>
-    <t>NQ-R16-BR-100002</t>
-  </si>
-  <si>
-    <t>NQ-R16-BR-100003</t>
-  </si>
-  <si>
     <t>RT-R16-BR-10000</t>
   </si>
   <si>
@@ -1375,7 +1366,19 @@
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.28515625" customWidth="1"/>
-    <col min="2" max="14" width="8.7109375" customWidth="1"/>
+    <col min="2" max="2" width="8.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.7109375" customWidth="1"/>
     <col min="15" max="15" width="31.7109375" customWidth="1"/>
     <col min="16" max="26" width="8.7109375" customWidth="1"/>
   </cols>
@@ -1487,7 +1490,7 @@
         <v>6</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>7</v>
@@ -1502,7 +1505,7 @@
         <v>10</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="M16" s="1" t="s">
         <v>11</v>
@@ -1531,7 +1534,7 @@
         <v>6</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>7</v>
@@ -1546,7 +1549,7 @@
         <v>10</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="M17" s="1" t="s">
         <v>11</v>
@@ -1575,7 +1578,7 @@
         <v>6</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>7</v>
@@ -1590,7 +1593,7 @@
         <v>10</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="M18" s="1" t="s">
         <v>11</v>
@@ -1619,7 +1622,7 @@
         <v>6</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>7</v>
@@ -1634,7 +1637,7 @@
         <v>10</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="M19" s="1" t="s">
         <v>11</v>
@@ -1708,7 +1711,7 @@
         <v>21</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>22</v>
@@ -1749,7 +1752,7 @@
         <v>21</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>22</v>
@@ -1790,7 +1793,7 @@
         <v>21</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>22</v>
